--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.40901580117687</v>
+        <v>3.316465067691242</v>
       </c>
       <c r="D2" t="n">
-        <v>20.38510494021458</v>
+        <v>3.312579552784869</v>
       </c>
       <c r="E2" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F2" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.68454770627039</v>
+        <v>1.736239002268938</v>
       </c>
       <c r="D3" t="n">
-        <v>10.74337931582382</v>
+        <v>1.745799138821371</v>
       </c>
       <c r="E3" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F3" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.40664464313472</v>
+        <v>4.453579754509392</v>
       </c>
       <c r="D4" t="n">
-        <v>27.40438057113213</v>
+        <v>4.453211842808972</v>
       </c>
       <c r="E4" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F4" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.86444983223485</v>
+        <v>5.340473097738164</v>
       </c>
       <c r="D5" t="n">
-        <v>32.66819935546803</v>
+        <v>5.308582395263555</v>
       </c>
       <c r="E5" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F5" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.06775135194574</v>
+        <v>6.348509594691182</v>
       </c>
       <c r="D6" t="n">
-        <v>38.71134343106716</v>
+        <v>6.290593307548413</v>
       </c>
       <c r="E6" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F6" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.8324001674846</v>
+        <v>2.572765027216247</v>
       </c>
       <c r="D7" t="n">
-        <v>15.99626191273291</v>
+        <v>2.599392560819098</v>
       </c>
       <c r="E7" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F7" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.74955270793328</v>
+        <v>5.484302315039159</v>
       </c>
       <c r="D8" t="n">
-        <v>33.99719160916209</v>
+        <v>5.524543636488841</v>
       </c>
       <c r="E8" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F8" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.20984145504344</v>
+        <v>4.259099236444559</v>
       </c>
       <c r="D9" t="n">
-        <v>25.63643604067703</v>
+        <v>4.165920856610017</v>
       </c>
       <c r="E9" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F9" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.66132728814466</v>
+        <v>1.894965684323507</v>
       </c>
       <c r="D10" t="n">
-        <v>10.57402482317726</v>
+        <v>1.718279033766305</v>
       </c>
       <c r="E10" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F10" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.543650595969095</v>
+        <v>1.225843221844978</v>
       </c>
       <c r="D11" t="n">
-        <v>8.530292100163388</v>
+        <v>1.386172466276551</v>
       </c>
       <c r="E11" t="n">
-        <v>10.37249987182731</v>
+        <v>1.685531229171938</v>
       </c>
       <c r="F11" t="n">
-        <v>10.26953837031077</v>
+        <v>1.6687999851755</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
